--- a/artfynd/A 32460-2024 artfynd.xlsx
+++ b/artfynd/A 32460-2024 artfynd.xlsx
@@ -2984,10 +2984,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119515616</v>
+        <v>119511973</v>
       </c>
       <c r="B24" t="n">
-        <v>79642</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2996,20 +2996,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3018,19 +3018,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Frödhöjden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>605725</v>
+        <v>605670</v>
       </c>
       <c r="R24" t="n">
-        <v>7038982</v>
+        <v>7039029</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3071,7 +3068,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3090,10 +3086,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119515444</v>
+        <v>119515616</v>
       </c>
       <c r="B25" t="n">
-        <v>100144</v>
+        <v>79642</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3106,27 +3102,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1365</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3134,13 +3129,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>605796</v>
+        <v>605725</v>
       </c>
       <c r="R25" t="n">
-        <v>7038974</v>
+        <v>7038982</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3197,10 +3192,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119511973</v>
+        <v>119515444</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>100144</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3209,41 +3204,45 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Frödhöjden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>605670</v>
+        <v>605796</v>
       </c>
       <c r="R26" t="n">
-        <v>7039029</v>
+        <v>7038974</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3281,6 +3280,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 32460-2024 artfynd.xlsx
+++ b/artfynd/A 32460-2024 artfynd.xlsx
@@ -2984,10 +2984,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119511973</v>
+        <v>119515616</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>79642</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2996,20 +2996,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3018,16 +3018,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Frödhöjden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>605670</v>
+        <v>605725</v>
       </c>
       <c r="R24" t="n">
-        <v>7039029</v>
+        <v>7038982</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3068,6 +3071,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3086,10 +3090,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119515616</v>
+        <v>119515444</v>
       </c>
       <c r="B25" t="n">
-        <v>79642</v>
+        <v>100144</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3102,26 +3106,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>1365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3129,13 +3134,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>605725</v>
+        <v>605796</v>
       </c>
       <c r="R25" t="n">
-        <v>7038982</v>
+        <v>7038974</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3192,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119515444</v>
+        <v>119511973</v>
       </c>
       <c r="B26" t="n">
-        <v>100144</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3204,45 +3209,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Frödhöjden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>605796</v>
+        <v>605670</v>
       </c>
       <c r="R26" t="n">
-        <v>7038974</v>
+        <v>7039029</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3280,7 +3281,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 32460-2024 artfynd.xlsx
+++ b/artfynd/A 32460-2024 artfynd.xlsx
@@ -1495,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119515304</v>
+        <v>119515550</v>
       </c>
       <c r="B10" t="n">
-        <v>100144</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,31 +1507,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1539,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>605725</v>
+        <v>605883</v>
       </c>
       <c r="R10" t="n">
-        <v>7039001</v>
+        <v>7038940</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1602,10 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119515524</v>
+        <v>119515593</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>86878</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,21 +1617,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1645,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>605850</v>
+        <v>605828</v>
       </c>
       <c r="R11" t="n">
-        <v>7038976</v>
+        <v>7038906</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1708,10 +1707,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119515574</v>
+        <v>119515616</v>
       </c>
       <c r="B12" t="n">
-        <v>90527</v>
+        <v>79642</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1724,21 +1723,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1751,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>605899</v>
+        <v>605725</v>
       </c>
       <c r="R12" t="n">
-        <v>7038929</v>
+        <v>7038982</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1814,10 +1813,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119515474</v>
+        <v>119515533</v>
       </c>
       <c r="B13" t="n">
-        <v>100144</v>
+        <v>57463</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1826,31 +1825,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1365</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1858,13 +1861,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>605825</v>
+        <v>605883</v>
       </c>
       <c r="R13" t="n">
-        <v>7038975</v>
+        <v>7038940</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1902,7 +1905,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1921,7 +1923,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119515346</v>
+        <v>119515474</v>
       </c>
       <c r="B14" t="n">
         <v>100144</v>
@@ -1965,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>605740</v>
+        <v>605825</v>
       </c>
       <c r="R14" t="n">
-        <v>7039005</v>
+        <v>7038975</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2028,7 +2030,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119515361</v>
+        <v>119515444</v>
       </c>
       <c r="B15" t="n">
         <v>100144</v>
@@ -2072,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>605757</v>
+        <v>605796</v>
       </c>
       <c r="R15" t="n">
-        <v>7038979</v>
+        <v>7038974</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,10 +2137,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119515593</v>
+        <v>119515603</v>
       </c>
       <c r="B16" t="n">
-        <v>86878</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2151,21 +2153,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2180,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>605828</v>
+        <v>605840</v>
       </c>
       <c r="R16" t="n">
-        <v>7038906</v>
+        <v>7038919</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2241,10 +2243,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119515550</v>
+        <v>119515361</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>100144</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2253,30 +2255,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2284,13 +2287,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>605883</v>
+        <v>605757</v>
       </c>
       <c r="R17" t="n">
-        <v>7038940</v>
+        <v>7038979</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2347,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119515603</v>
+        <v>119515537</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2359,25 +2362,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2390,10 +2393,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>605840</v>
+        <v>605883</v>
       </c>
       <c r="R18" t="n">
-        <v>7038919</v>
+        <v>7038940</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2453,10 +2456,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119515614</v>
+        <v>119515304</v>
       </c>
       <c r="B19" t="n">
-        <v>79607</v>
+        <v>100144</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2465,30 +2468,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1365</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2499,7 +2503,7 @@
         <v>605725</v>
       </c>
       <c r="R19" t="n">
-        <v>7038982</v>
+        <v>7039001</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2559,10 +2563,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119511972</v>
+        <v>119515524</v>
       </c>
       <c r="B20" t="n">
-        <v>100144</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2571,38 +2575,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Frödhöjden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>605652</v>
+        <v>605850</v>
       </c>
       <c r="R20" t="n">
-        <v>7039028</v>
+        <v>7038976</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2643,6 +2650,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2661,10 +2669,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119515566</v>
+        <v>119511972</v>
       </c>
       <c r="B21" t="n">
-        <v>90562</v>
+        <v>100144</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2673,41 +2681,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>1365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Frödhöjden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>605911</v>
+        <v>605652</v>
       </c>
       <c r="R21" t="n">
-        <v>7038967</v>
+        <v>7039028</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2748,7 +2753,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2767,10 +2771,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119515332</v>
+        <v>119511973</v>
       </c>
       <c r="B22" t="n">
-        <v>97928</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2779,45 +2783,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Frödhöjden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>605739</v>
+        <v>605670</v>
       </c>
       <c r="R22" t="n">
-        <v>7038990</v>
+        <v>7039029</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2855,7 +2855,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2874,10 +2873,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119515533</v>
+        <v>119515566</v>
       </c>
       <c r="B23" t="n">
-        <v>57463</v>
+        <v>90562</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2890,31 +2889,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2922,10 +2916,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>605883</v>
+        <v>605911</v>
       </c>
       <c r="R23" t="n">
-        <v>7038940</v>
+        <v>7038967</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2966,6 +2960,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2984,10 +2979,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119515616</v>
+        <v>119515332</v>
       </c>
       <c r="B24" t="n">
-        <v>79642</v>
+        <v>97928</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3000,26 +2995,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3027,13 +3023,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>605725</v>
+        <v>605739</v>
       </c>
       <c r="R24" t="n">
-        <v>7038982</v>
+        <v>7038990</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3090,7 +3086,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119515444</v>
+        <v>119515346</v>
       </c>
       <c r="B25" t="n">
         <v>100144</v>
@@ -3134,10 +3130,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>605796</v>
+        <v>605740</v>
       </c>
       <c r="R25" t="n">
-        <v>7038974</v>
+        <v>7039005</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3197,10 +3193,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119511973</v>
+        <v>119515614</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3213,34 +3209,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Frödhöjden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>605670</v>
+        <v>605725</v>
       </c>
       <c r="R26" t="n">
-        <v>7039029</v>
+        <v>7038982</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3281,6 +3280,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3299,7 +3299,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119515537</v>
+        <v>119515574</v>
       </c>
       <c r="B27" t="n">
         <v>90527</v>
@@ -3342,10 +3342,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>605883</v>
+        <v>605899</v>
       </c>
       <c r="R27" t="n">
-        <v>7038940</v>
+        <v>7038929</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>

--- a/artfynd/A 32460-2024 artfynd.xlsx
+++ b/artfynd/A 32460-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119325678</v>
+        <v>119325685</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>605890</v>
+        <v>605820</v>
       </c>
       <c r="R2" t="n">
-        <v>7038945</v>
+        <v>7038910</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119325679</v>
+        <v>119515593</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +783,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Frödhöjden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605862</v>
+        <v>605828</v>
       </c>
       <c r="R3" t="n">
-        <v>7038954</v>
+        <v>7038906</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +840,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,72 +854,64 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119325675</v>
+        <v>119325670</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Frödhöjden, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>605728</v>
+        <v>605935</v>
       </c>
       <c r="R4" t="n">
-        <v>7038935</v>
+        <v>7038896</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,53 +970,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119325669</v>
+        <v>119515566</v>
       </c>
       <c r="B5" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Frödhöjden, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>605834</v>
+        <v>605911</v>
       </c>
       <c r="R5" t="n">
-        <v>7038914</v>
+        <v>7038967</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1038,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1069,55 +1052,51 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119325676</v>
+        <v>119511972</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,13 +1106,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605994</v>
+        <v>605652</v>
       </c>
       <c r="R6" t="n">
-        <v>7038874</v>
+        <v>7039028</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1136,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,65 +1156,64 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119325685</v>
+        <v>119515304</v>
       </c>
       <c r="B7" t="n">
-        <v>86878</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>1365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Frödhöjden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605820</v>
+        <v>605725</v>
       </c>
       <c r="R7" t="n">
-        <v>7038910</v>
+        <v>7039001</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1259,12 +1237,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1273,71 +1251,71 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119325670</v>
+        <v>119515346</v>
       </c>
       <c r="B8" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Frödhöjden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>605935</v>
+        <v>605740</v>
       </c>
       <c r="R8" t="n">
-        <v>7038896</v>
+        <v>7039005</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1361,12 +1339,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1375,71 +1353,71 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119325683</v>
+        <v>119515361</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Frödhöjden, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>605993</v>
+        <v>605757</v>
       </c>
       <c r="R9" t="n">
-        <v>7038872</v>
+        <v>7038979</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1463,12 +1441,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1477,60 +1455,57 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119515550</v>
+        <v>119515444</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1538,13 +1513,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>605883</v>
+        <v>605796</v>
       </c>
       <c r="R10" t="n">
-        <v>7038940</v>
+        <v>7038974</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,42 +1576,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119515593</v>
+        <v>119515474</v>
       </c>
       <c r="B11" t="n">
-        <v>86878</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>1365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1644,13 +1615,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>605828</v>
+        <v>605825</v>
       </c>
       <c r="R11" t="n">
-        <v>7038906</v>
+        <v>7038975</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1707,15 +1678,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119515616</v>
+        <v>119325669</v>
       </c>
       <c r="B12" t="n">
-        <v>79642</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1723,40 +1689,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Frödhöjden, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>605725</v>
+        <v>605834</v>
       </c>
       <c r="R12" t="n">
-        <v>7038982</v>
+        <v>7038914</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1780,12 +1743,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1794,66 +1757,55 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119515533</v>
+        <v>119515537</v>
       </c>
       <c r="B13" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1905,6 +1857,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1923,15 +1876,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119515474</v>
+        <v>119515574</v>
       </c>
       <c r="B14" t="n">
-        <v>100144</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,27 +1887,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1365</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1967,13 +1914,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>605825</v>
+        <v>605899</v>
       </c>
       <c r="R14" t="n">
-        <v>7038975</v>
+        <v>7038929</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2030,57 +1977,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119515444</v>
+        <v>105166052</v>
       </c>
       <c r="B15" t="n">
-        <v>100144</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Frödhöjden, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>605796</v>
+        <v>605847</v>
       </c>
       <c r="R15" t="n">
-        <v>7038974</v>
+        <v>7038879</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2104,12 +2042,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-10-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-10-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2118,38 +2056,36 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119515603</v>
+        <v>119325680</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2171,22 +2107,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Frödhöjden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>605840</v>
+        <v>606048</v>
       </c>
       <c r="R16" t="n">
-        <v>7038919</v>
+        <v>7038813</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2210,12 +2143,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2224,76 +2157,66 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119515361</v>
+        <v>119325683</v>
       </c>
       <c r="B17" t="n">
-        <v>100144</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Frödhöjden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>605757</v>
+        <v>605993</v>
       </c>
       <c r="R17" t="n">
-        <v>7038979</v>
+        <v>7038872</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2317,12 +2240,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2331,72 +2254,63 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119515537</v>
+        <v>119511973</v>
       </c>
       <c r="B18" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Frödhöjden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>605883</v>
+        <v>605670</v>
       </c>
       <c r="R18" t="n">
-        <v>7038940</v>
+        <v>7039029</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2437,7 +2351,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2456,43 +2369,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119515304</v>
+        <v>119515524</v>
       </c>
       <c r="B19" t="n">
-        <v>100144</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2500,10 +2407,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>605725</v>
+        <v>605850</v>
       </c>
       <c r="R19" t="n">
-        <v>7039001</v>
+        <v>7038976</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2563,19 +2470,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119515524</v>
+        <v>119515550</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2606,10 +2508,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>605850</v>
+        <v>605883</v>
       </c>
       <c r="R20" t="n">
-        <v>7038976</v>
+        <v>7038940</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2669,50 +2571,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119511972</v>
+        <v>119515603</v>
       </c>
       <c r="B21" t="n">
-        <v>100144</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Frödhöjden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>605652</v>
+        <v>605840</v>
       </c>
       <c r="R21" t="n">
-        <v>7039028</v>
+        <v>7038919</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2753,6 +2653,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2771,15 +2672,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119511973</v>
+        <v>119515614</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2787,34 +2683,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Frödhöjden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>605670</v>
+        <v>605725</v>
       </c>
       <c r="R22" t="n">
-        <v>7039029</v>
+        <v>7038982</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2855,6 +2754,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2873,37 +2773,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119515566</v>
+        <v>119515616</v>
       </c>
       <c r="B23" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2916,10 +2811,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>605911</v>
+        <v>605725</v>
       </c>
       <c r="R23" t="n">
-        <v>7038967</v>
+        <v>7038982</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2979,57 +2874,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119515332</v>
+        <v>119325672</v>
       </c>
       <c r="B24" t="n">
-        <v>97928</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Frödhöjden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>605739</v>
+        <v>606050</v>
       </c>
       <c r="R24" t="n">
-        <v>7038990</v>
+        <v>7038812</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3053,12 +2944,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3067,62 +2958,60 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119515346</v>
+        <v>119515533</v>
       </c>
       <c r="B25" t="n">
-        <v>100144</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1365</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3130,13 +3019,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>605740</v>
+        <v>605883</v>
       </c>
       <c r="R25" t="n">
-        <v>7039005</v>
+        <v>7038940</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3174,7 +3063,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3193,56 +3081,52 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119515614</v>
+        <v>119325675</v>
       </c>
       <c r="B26" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Frödhöjden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>605725</v>
+        <v>605728</v>
       </c>
       <c r="R26" t="n">
-        <v>7038982</v>
+        <v>7038935</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3266,12 +3150,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3280,34 +3164,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119515574</v>
+        <v>119515332</v>
       </c>
       <c r="B27" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3315,26 +3193,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3342,13 +3221,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>605899</v>
+        <v>605739</v>
       </c>
       <c r="R27" t="n">
-        <v>7038929</v>
+        <v>7038990</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>

--- a/artfynd/A 32460-2024 artfynd.xlsx
+++ b/artfynd/A 32460-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119325685</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119515593</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119325670</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119515566</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119511972</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1267,6 +1297,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119515304</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119515346</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1471,6 +1511,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119515361</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1573,6 +1618,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119515444</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1675,6 +1725,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119515474</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1772,6 +1827,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119325669</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1873,6 +1933,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119515537</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1974,6 +2039,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119515574</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2075,6 +2145,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166052</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2172,6 +2247,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119325680</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2269,6 +2349,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119325683</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2366,6 +2451,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119511973</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2467,6 +2557,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119515524</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2568,6 +2663,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119515550</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2669,6 +2769,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119515603</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2770,6 +2875,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119515614</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2871,6 +2981,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119515616</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2973,6 +3088,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119325672</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3078,6 +3198,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119515533</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3179,6 +3304,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119325675</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3281,8 +3411,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119515332</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>